--- a/Data/MaHH.xlsx
+++ b/Data/MaHH.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_BB\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94381FB8-ADB9-4601-BDE2-8FCA8417E6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8180AFE7-95A4-41F6-8FEE-FFA67EF4F3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1154C90-8187-4C9D-8DDB-7618463980C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>HH034</t>
   </si>
@@ -69,6 +56,12 @@
   </si>
   <si>
     <t>VCF mùa đông</t>
+  </si>
+  <si>
+    <t>Xăng E10 RON95 Mức 3</t>
+  </si>
+  <si>
+    <t>HH051</t>
   </si>
 </sst>
 </file>
@@ -785,9 +778,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -825,7 +818,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -931,7 +924,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1073,7 +1066,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1081,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9639D367-352F-44BE-8505-63CC30B1FB0F}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1160,6 +1153,20 @@
         <v>0.98250000000000004</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.99150000000000005</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.98250000000000004</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
